--- a/docs/weekly/주간업무_5주차_2026-08-24_08-28.xlsx
+++ b/docs/weekly/주간업무_5주차_2026-08-24_08-28.xlsx
@@ -478,32 +478,29 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>- 퇴직연금 사후관리 에이전트 구현 통합 및 시연 데이터 정비
-  ㅇ 여러 세션 브랜치에 흩어져 있던 에이전트 구현(src)을 main 으로 통합
-  ㅇ 더미 고객 페르소나 폐기 후 시연용 9케이스 적재, 고객 원장의 재료(자산군별 금액, ISA 만기자금, 납입이력, 보유상품, 상담이력 등)를 대화형까지 연결
-  ㅇ 타겟 룰베이스(기획자 확인표)를 타겟 선정 임계값의 상위 기준으로 도입
-- 코어 비즈니스 로직 지식 정제
-  ㅇ 판단 3단계 구조로 전면 재편, 상태 판정 룰·액션·도메인지식의 단일 정의처 신설
-  ㅇ 행내 원천문서 정독 4라운드 반영(이탈방지상담, 운용·수익률, 디폴트옵션 공문, 리밸런싱 마케팅, 마케팅 추진 Tip)
-- 답변 근거 신뢰성 및 지식 검색 품질 개선
-  ㅇ 시황·상품 기반지식 적재 및 상품 질의 라우팅 게이트 교정
-  ㅇ 카드가 소속·신원으로 자료 성격을 추론하던 문장 제거, 인용 수치·날짜 검증 정규화
-  ㅇ 원장 기준일과 상담 시점 «오늘» 의 시간축 분리
-- 대화형 응답 성능·품질 개선
-  ㅇ 되묻기 판정과 답변 작성 동시 실행, 브리핑 캐시 적용으로 턴 지연 단축
-  ㅇ 고객 상태별 화법 제시(playbook) 및 답변 말미 추천질문 기능 개발
-  ㅇ 실행 트레이스 하네스·디버그 CLI 구축으로 답변이 갈리는 지점 추적 가능하도록 함</t>
+          <t>- 에이전트 구현 통합 및 시연 데이터 정비
+  ㅇ 분산 개발된 에이전트 구현을 단일 브랜치로 통합
+  ㅇ 시연용 고객 9케이스 적재 및 고객 데이터(보유상품, 수익률, 만기, 납입이력 등) 연동
+  ㅇ 타겟 선정 임계값을 기획 확정 룰베이스 기준으로 일괄 반영
+- 코어 비즈니스 로직 정비
+  ㅇ 판단 로직을 3단계 구조로 재편, 상태 판정 룰·액션·도메인지식 정의서 신설
+  ㅇ 행내 원천문서 4개 분야 반영(이탈방지상담, 운용·수익률, 디폴트옵션, 리밸런싱 마케팅)
+- 답변 정확도 개선
+  ㅇ 시황·상품 지식 적재 및 상품 질의 라우팅 오류 수정
+  ㅇ 인용 수치·날짜 검증 로직 보완, 데이터 기준일과 상담일 분리 적용
+- 응답 속도 및 대화 품질 개선
+  ㅇ 판정·답변 생성 병렬 처리 및 결과 캐싱으로 응답 지연 단축
+  ㅇ 고객 상태별 화법 제시, 답변 말미 추천질문 기능 개발</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>- 실서비스 전환 위험 항목 조치
-  ㅇ 상담이력 저장소 원자적 쓰기·고객 단위 잠금 적용(동시 상담 시 상담 턴 유실 방지)
-  ㅇ 브리핑 공유 구조 정리(단일 프로세스 전제 제거)
-- 더미 데이터의 실물 전환
-  ㅇ 안내 콘텐츠·금리표 등 자리표시자를 실제 소스로 연결
-- 타겟 룰베이스 근거등급 D(행내 원문에 없는 기획자 설계 제안) 의존 지점 정리 및 화면 표기 방침 확정
-- 세액공제 환급 예상액 계산기 확장(잔여 계산 항목 반영)
+          <t>- 실서비스 전환 대비 조치
+  ㅇ 상담이력 저장 시 동시 접근 제어 적용(상담 내역 유실 방지)
+  ㅇ 단일 프로세스 전제로 구성된 데이터 공유 구조 개선
+- 시연용 더미 데이터(안내 콘텐츠, 금리 정보)를 실제 소스로 연동
+- 타겟 룰베이스 미확정 항목 정리 및 화면 표기 기준 확정
+- 세액공제 환급액 계산 기능 확장
 - 고객 페르소나 9케이스 기반 에이전트 답변 품질 테스트</t>
         </is>
       </c>
@@ -516,9 +513,9 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>- 에이전트가 고객 수치를 답변에 옮길 때 표기 차이만으로 검증기에서 폐기되는 문제가 있었음(15.0%와 15%, "148만 5천원"과 "1,485,000원"을 다른 값으로 판정). 이에 수치를 값 보존 정규형으로 바꾸고 덩이 단위로 대조하도록 검증 로직을 개선하여 해결함.
-- 원장 기준일과 실제 상담일이 뒤섞여 만기 잔여일수·경과일이 어긋나는 문제가 있었음. 이에 시간축을 원장 기준일과 상담 시점 «오늘» 로 분리하고, 검증기가 날짜를 통짜로 대조하도록 하여 해결함.
-- 지식베이스 원문 중 시황·상품 폴더만 적재 경로가 없어 상품 질의가 브리핑 덤프로 끝나는 문제가 있었음. 해당 폴더를 적재하고 표를 관계로 선언하여 검색 입구를 통일함으로써 해결함.</t>
+          <t>- 동일한 수치를 표기만 다르게 쓴 경우(15.0%와 15%, "148만 5천원"과 "1,485,000원") 검증 단계에서 오답으로 처리되는 문제가 있었음. 수치를 정규화한 후 비교하도록 검증 로직을 수정하여 해결함.
+- 데이터 기준일과 실제 상담일이 구분되지 않아 만기 잔여일수가 잘못 산출되는 문제가 있었음. 두 기준을 분리하고 날짜 검증 로직을 보완하여 해결함.
+- 시황·상품 자료가 지식베이스에 적재되지 않아 상품 질의에 정상 응답하지 못하는 문제가 있었음. 해당 자료를 적재하고 검색 경로를 일원화하여 해결함.</t>
         </is>
       </c>
       <c r="D4" s="3" t="n"/>
